--- a/data/trans_orig/IP31KM11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM11_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>119991</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>115320</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>122027</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>111982</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>107616</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>113620</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>128960</t>
+          <t>116074</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104734</t>
+          <t>110999</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135727</t>
+          <t>117927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>240942</t>
+          <t>236065</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219749</t>
+          <t>229816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247969</t>
+          <t>239516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32081</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31317</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>226832</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>221835</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>229408</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>183235</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>179556</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>185123</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>242652</t>
+          <t>177669</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>236379</t>
+          <t>174129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>245450</t>
+          <t>179585</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>425887</t>
+          <t>404500</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>419874</t>
+          <t>398214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>429470</t>
+          <t>407718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4409</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1833</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9406</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2879</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6558</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>162183</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>155373</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>165192</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>155038</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>178754</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>171146</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>181921</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>93,48%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>439</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>367004</t>
+          <t>317221</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>359351</t>
+          <t>310350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>370333</t>
+          <t>320562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4339</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11149</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4335</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1168</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11943</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>161079</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>155809</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>163730</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>162794</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>159675</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>164023</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>172479</t>
+          <t>162296</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167410</t>
+          <t>159372</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175215</t>
+          <t>163525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>335273</t>
+          <t>323375</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>330214</t>
+          <t>317900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>338591</t>
+          <t>326798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5086</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2435</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10356</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4844</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>670086</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>662166</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>676812</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>904</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>646262</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>640876</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>649796</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>722845</t>
+          <t>611077</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>699061</t>
+          <t>605353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>731853</t>
+          <t>614642</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1369107</t>
+          <t>1281162</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1347114</t>
+          <t>1271295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1379103</t>
+          <t>1288578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24658</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6872</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12258</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50753</t>
+          <t>33736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
